--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_TRANCOSO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_TRANCOSO_pgto_05-10-2026.xlsx
@@ -1965,9 +1965,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15">
-        <f> COMISSÃO TOTAL</f>
-        <v/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>COMISSÃO TOTAL (soma)</t>
+        </is>
       </c>
       <c r="B11" s="20">
         <f>SUM(B9:B10)</f>
@@ -2029,9 +2030,10 @@
         <f>SUM(B12:F12)</f>
         <v/>
       </c>
-      <c r="H12" s="29">
-        <f> (comissão total + horas extras) × (4 domingos + feriado 07/09) ÷ 25 dias úteis de setembro/2026.</f>
-        <v/>
+      <c r="H12" s="29" t="inlineStr">
+        <is>
+          <t>Cálculo: (comissão total + horas extras) × (4 domingos + feriado 07/09) ÷ 25 dias úteis de setembro/2026.</t>
+        </is>
       </c>
     </row>
     <row r="13">

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_TRANCOSO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_TRANCOSO_pgto_05-10-2026.xlsx
@@ -17,10 +17,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA SET.26'!$A$4:$J$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE SET.26'!$A$4:$H$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE SET.26'!$A$4:$H$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$128</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'GANHOS DO COLABORADOR'!$A$1:$D$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PONTO SET.26'!$A$4:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PONTO SET.26'!$A$4:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -654,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -851,22 +851,18 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>VALDICK: férias de 01 a 30/09/2026 (mês inteiro) — salário zerado; férias e 1/3 em recibo próprio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>PENDÊNCIAS — CONFIRMAR ANTES DE ENVIAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Horas extras, adicional noturno e feriados trabalhados de setembro — lançar na aba PONTO SET.26.</t>
         </is>
       </c>
     </row>
@@ -878,7 +874,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Prêmio cota geral e prêmio pré-vencidos, conforme a tabela de metas da loja.</t>
+          <t>Horas extras, adicional noturno e feriados trabalhados de setembro — lançar na aba PONTO SET.26.</t>
         </is>
       </c>
     </row>
@@ -890,7 +886,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Vales adiantados, convênio e faltas de agosto.</t>
+          <t>Prêmio cota geral e prêmio pré-vencidos, conforme a tabela de metas da loja.</t>
         </is>
       </c>
     </row>
@@ -902,7 +898,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Férias, afastamentos e admissões que mudem o salário do mês.</t>
+          <t>Vales adiantados, convênio e faltas de agosto.</t>
         </is>
       </c>
     </row>
@@ -914,7 +910,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Extrair o relatório de comissões de setembro no InovaFarma e preencher a aba BASE INOVAFARMA SET.26.</t>
+          <t>Férias, afastamentos e admissões que mudem o salário do mês.</t>
         </is>
       </c>
     </row>
@@ -926,7 +922,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>TAMILES: se o atestado for prorrogado além de 15 dias corridos, a partir do 16º dia passa a ser auxílio-doença do INSS.</t>
+          <t>Extrair o relatório de comissões de setembro no InovaFarma e preencher a aba BASE INOVAFARMA SET.26.</t>
         </is>
       </c>
     </row>
@@ -938,37 +934,41 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
+          <t>TAMILES: se o atestado for prorrogado além de 15 dias corridos, a partir do 16º dia passa a ser auxílio-doença do INSS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
           <t>Lançar na linha PRÊMIO COTA GERAL o valor já com a redução combinada.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO TÉCNICA</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="4" t="inlineStr"/>
-      <c r="B36" s="5" t="inlineStr">
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="4" t="inlineStr"/>
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>As células de total e de cálculo são fórmulas. Ao abrir no Excel ou no Google Planilhas elas aparecem calculadas; em visualizadores simples podem aparecer em branco até o arquivo ser aberto.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>ABAS DO ARQUIVO</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="4" t="inlineStr"/>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>HOLERITE SET.26 — relatório principal da competência setembro/2026.</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
+          <t>HOLERITE SET.26 — relatório principal da competência setembro/2026.</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       <c r="A40" s="4" t="inlineStr"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
+          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>BASE INOVAFARMA SET.26 — apuração de comissões e incentivos por vendedor.</t>
+          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
         </is>
       </c>
     </row>
@@ -1000,13 +1000,21 @@
       <c r="A42" s="4" t="inlineStr"/>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
+          <t>BASE INOVAFARMA SET.26 — apuração de comissões e incentivos por vendedor.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="4" t="inlineStr"/>
       <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="4" t="inlineStr"/>
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>PONTO SET.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
         </is>
@@ -1017,12 +1025,12 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1722,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1818,7 +1826,7 @@
         <v>1621</v>
       </c>
       <c r="D6" s="27" t="n">
-        <v>1621</v>
+        <v>0</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>1621</v>
@@ -1843,23 +1851,23 @@
         </is>
       </c>
       <c r="B7" s="30">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,B$4,'PONTO SET.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,B$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="C7" s="30">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,C$4,'PONTO SET.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,C$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="D7" s="30">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,D$4,'PONTO SET.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,D$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="E7" s="30">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,E$4,'PONTO SET.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,E$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="F7" s="30">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,F$4,'PONTO SET.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,F$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="G7" s="20">
@@ -1879,23 +1887,23 @@
         </is>
       </c>
       <c r="B8" s="30">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,B$4,'PONTO SET.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,B$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="C8" s="30">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,C$4,'PONTO SET.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,C$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="D8" s="30">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,D$4,'PONTO SET.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,D$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="E8" s="30">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,E$4,'PONTO SET.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,E$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="F8" s="30">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,F$4,'PONTO SET.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,F$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="G8" s="20">
@@ -2323,7 +2331,7 @@
     <row r="24">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="B24" s="31" t="n"/>
@@ -2620,71 +2628,92 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-      <c r="B38" s="35" t="inlineStr"/>
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>FÉRIAS PAGAS À PARTE (CONTAS A PAGAR)</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="28">
+        <f>SUM(B37:F37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="29" t="inlineStr">
+        <is>
+          <t>Recibo de férias pago fora do holerite — lembrete para o contas a pagar. VALDICK: férias de 01 a 30/09/2026 — informar o valor do recibo.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="inlineStr">
         <is>
-          <t>Célula amarela, texto azul</t>
-        </is>
-      </c>
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
-        </is>
-      </c>
+          <t>LEGENDA</t>
+        </is>
+      </c>
+      <c r="B39" s="35" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>Célula laranja</t>
+          <t>Célula amarela, texto azul</t>
         </is>
       </c>
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>valor repetido de agosto/2026 — CONFERIR se continua válido em setembro.</t>
+          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>Texto verde</t>
+          <t>Célula laranja</t>
         </is>
       </c>
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>valor puxado da aba BASE INOVAFARMA SET.26 (não digitar por cima).</t>
+          <t>valor repetido de agosto/2026 — CONFERIR se continua válido em setembro.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
         <is>
+          <t>Texto verde</t>
+        </is>
+      </c>
+      <c r="B42" s="35" t="inlineStr">
+        <is>
+          <t>valor puxado da aba BASE INOVAFARMA SET.26 (não digitar por cima).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
           <t>Texto preto em célula verde</t>
         </is>
       </c>
-      <c r="B42" s="35" t="inlineStr">
+      <c r="B43" s="35" t="inlineStr">
         <is>
           <t>resultado de fórmula — não alterar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H36"/>
+  <autoFilter ref="A4:H37"/>
   <mergeCells count="7">
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="B41:H41"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B38:H38"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3086,7 +3115,7 @@
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C20" s="26" t="inlineStr">
@@ -3614,7 +3643,7 @@
       </c>
       <c r="B45" s="26" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C45" s="26" t="inlineStr">
@@ -4142,7 +4171,7 @@
       </c>
       <c r="B70" s="26" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C70" s="26" t="inlineStr">
@@ -4670,7 +4699,7 @@
       </c>
       <c r="B95" s="26" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C95" s="26" t="inlineStr">
@@ -5198,7 +5227,7 @@
       </c>
       <c r="B120" s="26" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C120" s="26" t="inlineStr">
@@ -5630,7 +5659,7 @@
     <row r="23">
       <c r="B23" s="26" t="inlineStr">
         <is>
-          <t>Adiantamento / vales</t>
+          <t>Adiantamento salarial / vales</t>
         </is>
       </c>
       <c r="C23" s="30">
@@ -5846,7 +5875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5924,16 +5953,16 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>TAMILES</t>
+          <t>VALDICK</t>
         </is>
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>Atestado médico (abonado)</t>
+          <t>Registro informativo</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
@@ -5958,26 +5987,50 @@
       </c>
       <c r="I5" s="29" t="inlineStr">
         <is>
-          <t>Atestado médico de 02 a 08/09/2026, entregue em 02/09. Até 15 dias é abonado pela empresa: falta justificada, SEM desconto de salário nem de DSR. Anexar o atestado à pasta da funcionária.</t>
+          <t>Férias de 01 a 30/09/2026 — mês inteiro. Salário zerado no holerite; férias e 1/3 vão em recibo próprio.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="n"/>
-      <c r="B6" s="49" t="n"/>
-      <c r="C6" s="49" t="n"/>
-      <c r="D6" s="49" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Atestado médico (abonado)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>dias</t>
+        </is>
+      </c>
       <c r="E6" s="30">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A6,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F6" s="31" t="n"/>
+      <c r="F6" s="32" t="n">
+        <v>0</v>
+      </c>
       <c r="G6" s="20">
         <f>ROUND(C6*F6,2)</f>
         <v/>
       </c>
-      <c r="H6" s="49" t="n"/>
-      <c r="I6" s="49" t="n"/>
+      <c r="H6" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="29" t="inlineStr">
+        <is>
+          <t>Atestado médico de 02 a 08/09/2026, entregue em 02/09. Até 15 dias é abonado pela empresa: falta justificada, SEM desconto de salário nem de DSR. Anexar o atestado à pasta da funcionária.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="49" t="n"/>
@@ -6099,60 +6152,77 @@
       <c r="I13" s="49" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n"/>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="A14" s="49" t="n"/>
+      <c r="B14" s="49" t="n"/>
+      <c r="C14" s="49" t="n"/>
+      <c r="D14" s="49" t="n"/>
+      <c r="E14" s="30">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A14,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="31" t="n"/>
+      <c r="G14" s="20">
+        <f>ROUND(C14*F14,2)</f>
+        <v/>
+      </c>
+      <c r="H14" s="49" t="n"/>
+      <c r="I14" s="49" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="n"/>
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="20">
-        <f>SUM(G5:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="18" t="n"/>
-      <c r="I14" s="18" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Salário-hora = salário base ÷ 220. Hora extra = salário-hora × 1,5. Adicional noturno = salário-hora × 20%. Feriado trabalhado sem folga = 1 salário-dia a mais (salário base ÷ 30).</t>
-        </is>
-      </c>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="20">
+        <f>SUM(G5:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>No salário de R$ 1.621,00: 40 horas extras dão R$ 442,09 e 24 horas dão R$ 265,25 — é a mesma conta usada na planilha de julho.</t>
+          <t>Salário-hora = salário base ÷ 220. Hora extra = salário-hora × 1,5. Adicional noturno = salário-hora × 20%. Feriado trabalhado sem folga = 1 salário-dia a mais (salário base ÷ 30).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>As linhas em branco são para acrescentar ocorrências: preencha funcionário, ocorrência, quantidade, valor unitário e a rubrica de destino (HORAS EXTRAS ou ADICIONAL NOTURNO).</t>
+          <t>No salário de R$ 1.621,00: 40 horas extras dão R$ 442,09 e 24 horas dão R$ 265,25 — é a mesma conta usada na planilha de julho.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
+          <t>As linhas em branco são para acrescentar ocorrências: preencha funcionário, ocorrência, quantidade, valor unitário e a rubrica de destino (HORAS EXTRAS ou ADICIONAL NOTURNO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
           <t>Os totais desta aba entram sozinhos nas linhas HORAS EXTRAS e ADICIONAL NOTURNO da aba HOLERITE SET.26.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I13"/>
+  <autoFilter ref="A4:I14"/>
   <mergeCells count="6">
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A20:I20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
